--- a/02_Zero_Shot/outputs/Embedding/DistilBERT-base-uncased/RESULT_f-droid_distilbert-base-uncased_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/DistilBERT-base-uncased/RESULT_f-droid_distilbert-base-uncased_zeroshot.xlsx
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.332704849999573</v>
+        <v>15.40963825599829</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002229040777894957</v>
+        <v>0.005424019097500277</v>
       </c>
     </row>
   </sheetData>
